--- a/GenBOE/GenBOE.Web/Templates/Export/WBSs.xlsx
+++ b/GenBOE/GenBOE.Web/Templates/Export/WBSs.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D0350F-53E3-43A2-9DF0-6F98C53DD726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1392" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="38280" yWindow="-75" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -14,12 +15,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -34,7 +35,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -48,7 +49,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -61,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -98,7 +99,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -188,7 +189,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="genBOE" xfId="1"/>
+    <cellStyle name="genBOE" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -205,9 +206,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -245,9 +246,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -282,7 +283,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -317,7 +318,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -490,16 +491,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="31.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="31.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="2" max="4" width="31.88671875" style="3"/>
-    <col min="5" max="16384" width="31.88671875" style="1"/>
+    <col min="2" max="4" width="31.85546875" style="3"/>
+    <col min="5" max="16384" width="31.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="2" customFormat="1" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -513,10 +514,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.4" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:4" ht="13.5" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Lockheed Martin Proprietary Information</oddFooter>
+  </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>